--- a/be/src/mindbody/fixtures/reports/Clients/17 Schedule at a Glance/17 Schedule at a Glance - 2090.xlsx
+++ b/be/src/mindbody/fixtures/reports/Clients/17 Schedule at a Glance/17 Schedule at a Glance - 2090.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -314,6 +314,36 @@
   </si>
   <si>
     <t xml:space="preserve">Reserved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hatha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instructor, Ivy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studio 1 - Hot Room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Hall </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doe, Jane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91234567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Late Cancel</t>
   </si>
   <si>
     <t xml:space="preserve">Client</t>
@@ -788,6 +818,53 @@
         <v>102</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11">
+        <v>46209</v>
+      </c>
+      <c r="B11">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="C11">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" t="s">
+        <v>106</v>
+      </c>
+      <c r="I11" t="s">
+        <v>107</v>
+      </c>
+      <c r="J11" t="s">
+        <v>108</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>6</v>
+      </c>
+      <c r="M11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N11" t="s">
+        <v>110</v>
+      </c>
+      <c r="O11" t="s">
+        <v>111</v>
+      </c>
+      <c r="P11" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>